--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-11.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="G2" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
         <v>4.1</v>
@@ -784,7 +784,7 @@
         <v>3.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
         <v>2.04</v>
@@ -793,34 +793,34 @@
         <v>1.83</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S2" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="T2" t="n">
         <v>1.75</v>
       </c>
       <c r="U2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
         <v>17.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA2" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
         <v>11.5</v>
@@ -829,7 +829,7 @@
         <v>10</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE2" t="n">
         <v>65</v>
@@ -844,7 +844,7 @@
         <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ2" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
         <v>13.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP2" t="n">
         <v>14</v>
@@ -871,13 +871,13 @@
         <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AU2" t="n">
         <v>7.6</v>
@@ -886,19 +886,19 @@
         <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX2" t="n">
         <v>9.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
         <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB2" t="n">
         <v>16</v>
@@ -907,20 +907,20 @@
         <v>15</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -954,28 +954,28 @@
         <v>2.2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.23</v>
@@ -984,13 +984,13 @@
         <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="R3" t="n">
         <v>1.48</v>
       </c>
       <c r="S3" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="T3" t="n">
         <v>1.61</v>
@@ -999,43 +999,43 @@
         <v>2.36</v>
       </c>
       <c r="V3" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W3" t="n">
         <v>1.81</v>
       </c>
       <c r="X3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Y3" t="n">
         <v>17</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH3" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>17</v>
       </c>
       <c r="AI3" t="n">
         <v>42</v>
@@ -1047,7 +1047,7 @@
         <v>22</v>
       </c>
       <c r="AL3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1062,59 +1062,59 @@
         <v>16</v>
       </c>
       <c r="AQ3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX3" t="n">
         <v>13.5</v>
       </c>
-      <c r="AR3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>13</v>
-      </c>
       <c r="AY3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BB3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD3" t="n">
         <v>22</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.2</v>
+        <v>55</v>
       </c>
       <c r="BF3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.2</v>
+        <v>23</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -1163,43 +1163,43 @@
         <v>4.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O4" t="n">
         <v>1.1</v>
       </c>
       <c r="P4" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="Q4" t="n">
         <v>1.32</v>
       </c>
       <c r="R4" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="T4" t="n">
         <v>1.35</v>
       </c>
       <c r="U4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="V4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
         <v>1.83</v>
       </c>
       <c r="X4" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
         <v>32</v>
@@ -1241,10 +1241,10 @@
         <v>23</v>
       </c>
       <c r="AL4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AN4" t="n">
         <v>7.4</v>
@@ -1253,16 +1253,16 @@
         <v>13.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.6</v>
+        <v>40</v>
       </c>
       <c r="AQ4" t="n">
         <v>24</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.8</v>
+        <v>40</v>
       </c>
       <c r="AT4" t="n">
         <v>20</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1342,10 @@
         <v>2.54</v>
       </c>
       <c r="G5" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H5" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="I5" t="n">
         <v>2.7</v>
@@ -1354,7 +1354,7 @@
         <v>3.85</v>
       </c>
       <c r="K5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1366,13 +1366,13 @@
         <v>5.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P5" t="n">
         <v>2.48</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="R5" t="n">
         <v>1.61</v>
@@ -1381,7 +1381,7 @@
         <v>2.38</v>
       </c>
       <c r="T5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U5" t="n">
         <v>2.6</v>
@@ -1390,7 +1390,7 @@
         <v>1.58</v>
       </c>
       <c r="W5" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X5" t="n">
         <v>29</v>
@@ -1405,7 +1405,7 @@
         <v>40</v>
       </c>
       <c r="AB5" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC5" t="n">
         <v>11.5</v>
@@ -1456,7 +1456,7 @@
         <v>18.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT5" t="n">
         <v>14</v>
@@ -1489,10 +1489,10 @@
         <v>21</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.6</v>
+        <v>20</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF5" t="n">
         <v>12.5</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         <v>3.45</v>
       </c>
       <c r="I8" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J8" t="n">
         <v>3.1</v>
@@ -1954,7 +1954,7 @@
         <v>1.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q10" t="n">
         <v>1.56</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G11" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H11" t="n">
         <v>3.45</v>
       </c>
       <c r="I11" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
         <v>3.85</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="G12" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H12" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="I12" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K12" t="n">
         <v>3.7</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q12" t="n">
         <v>2</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G13" t="n">
         <v>1.46</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q13" t="n">
         <v>1.51</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -3088,13 +3088,13 @@
         <v>2.14</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H14" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I14" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J14" t="n">
         <v>3.5</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>5.6</v>
       </c>
       <c r="I16" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J16" t="n">
         <v>4</v>
@@ -3506,7 +3506,7 @@
         <v>2.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -3673,16 +3673,16 @@
         <v>1.48</v>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>8.4</v>
       </c>
       <c r="J17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3709,7 +3709,7 @@
         <v>2.7</v>
       </c>
       <c r="T17" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U17" t="n">
         <v>2.08</v>
@@ -3733,7 +3733,7 @@
         <v>240</v>
       </c>
       <c r="AB17" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC17" t="n">
         <v>10.5</v>
@@ -3742,7 +3742,7 @@
         <v>30</v>
       </c>
       <c r="AE17" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF17" t="n">
         <v>9.4</v>
@@ -3769,7 +3769,7 @@
         <v>110</v>
       </c>
       <c r="AN17" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AO17" t="n">
         <v>120</v>
@@ -3817,7 +3817,7 @@
         <v>13.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE17" t="n">
         <v>90</v>
@@ -3826,11 +3826,11 @@
         <v>5.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
         <v>2.62</v>
       </c>
       <c r="H18" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I18" t="n">
         <v>3.05</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="G20" t="n">
         <v>1.91</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J20" t="n">
         <v>4.2</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G21" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="H21" t="n">
         <v>2.24</v>
@@ -4458,7 +4458,7 @@
         <v>3.05</v>
       </c>
       <c r="K21" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4467,16 +4467,16 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="O21" t="n">
         <v>1.45</v>
       </c>
       <c r="P21" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H22" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J22" t="n">
         <v>2.94</v>
@@ -4667,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -4855,13 +4855,13 @@
         <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O23" t="n">
         <v>1.32</v>
       </c>
       <c r="P23" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q23" t="n">
         <v>1.96</v>
@@ -4870,7 +4870,7 @@
         <v>1.37</v>
       </c>
       <c r="S23" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T23" t="n">
         <v>1.92</v>
@@ -4888,7 +4888,7 @@
         <v>14.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z23" t="n">
         <v>42</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G24" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="H24" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I24" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="J24" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -6383,16 +6383,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="G31" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="H31" t="n">
         <v>3.25</v>
       </c>
       <c r="I31" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="J31" t="n">
         <v>3</v>
@@ -6407,7 +6407,7 @@
         <v>1.1</v>
       </c>
       <c r="N31" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O31" t="n">
         <v>1.44</v>
@@ -6416,10 +6416,10 @@
         <v>1.64</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S31" t="n">
         <v>4.4</v>
@@ -6431,10 +6431,10 @@
         <v>1.9</v>
       </c>
       <c r="V31" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W31" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="X31" t="n">
         <v>11.5</v>
@@ -6449,7 +6449,7 @@
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC31" t="n">
         <v>8.199999999999999</v>
@@ -6461,7 +6461,7 @@
         <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG31" t="n">
         <v>14.5</v>
@@ -6473,10 +6473,10 @@
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK31" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL31" t="n">
         <v>1000</v>
@@ -6485,34 +6485,34 @@
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>3.65</v>
+        <v>7.6</v>
       </c>
       <c r="AQ31" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.4</v>
+        <v>18</v>
       </c>
       <c r="AS31" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AT31" t="n">
         <v>7</v>
       </c>
       <c r="AU31" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AV31" t="n">
-        <v>3.95</v>
+        <v>11.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AX31" t="n">
         <v>11.5</v>
@@ -6521,32 +6521,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.3</v>
+        <v>16.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB31" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BE31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF31" t="n">
         <v>5.1</v>
       </c>
-      <c r="BF31" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG31" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -7395,7 +7395,7 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U36" t="n">
         <v>1.88</v>
@@ -7410,22 +7410,22 @@
         <v>10</v>
       </c>
       <c r="Y36" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z36" t="n">
         <v>28</v>
       </c>
       <c r="AA36" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AB36" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC36" t="n">
         <v>7.4</v>
       </c>
       <c r="AD36" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE36" t="n">
         <v>65</v>
@@ -7434,7 +7434,7 @@
         <v>12.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH36" t="n">
         <v>22</v>
@@ -7446,7 +7446,7 @@
         <v>30</v>
       </c>
       <c r="AK36" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AL36" t="n">
         <v>55</v>
@@ -7461,16 +7461,16 @@
         <v>85</v>
       </c>
       <c r="AP36" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ36" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR36" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AS36" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AT36" t="n">
         <v>7</v>
@@ -7479,13 +7479,13 @@
         <v>6.6</v>
       </c>
       <c r="AV36" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AX36" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY36" t="n">
         <v>10.5</v>
@@ -7494,29 +7494,29 @@
         <v>18.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BB36" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BC36" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="BE36" t="n">
         <v>44</v>
       </c>
       <c r="BF36" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="BG36" t="n">
         <v>36</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7556,7 @@
         <v>3.45</v>
       </c>
       <c r="I37" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="J37" t="n">
         <v>3.2</v>
@@ -7577,7 +7577,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q37" t="n">
         <v>2.06</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -7741,19 +7741,19 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G38" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="H38" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I38" t="n">
         <v>3.4</v>
       </c>
       <c r="J38" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K38" t="n">
         <v>3.7</v>
@@ -7771,7 +7771,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q38" t="n">
         <v>2</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -7980,7 +7980,7 @@
         <v>2.16</v>
       </c>
       <c r="U39" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -8064,7 +8064,7 @@
         <v>18</v>
       </c>
       <c r="AW39" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="AX39" t="n">
         <v>9.6</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -8132,10 +8132,10 @@
         <v>2.98</v>
       </c>
       <c r="G40" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="H40" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I40" t="n">
         <v>2.76</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
         <v>1.56</v>
       </c>
       <c r="G43" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H43" t="n">
         <v>6</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -8938,19 +8938,19 @@
         <v>2.44</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="R44" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S44" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T44" t="n">
         <v>1.57</v>
       </c>
       <c r="U44" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -8959,7 +8959,7 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y44" t="n">
         <v>15.5</v>
@@ -9010,7 +9010,7 @@
         <v>16</v>
       </c>
       <c r="AO44" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AP44" t="n">
         <v>19.5</v>
@@ -9034,7 +9034,7 @@
         <v>11</v>
       </c>
       <c r="AW44" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AX44" t="n">
         <v>18</v>
@@ -9046,7 +9046,7 @@
         <v>13</v>
       </c>
       <c r="BA44" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BB44" t="n">
         <v>32</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="G47" t="n">
         <v>3.15</v>
@@ -9496,7 +9496,7 @@
         <v>2.48</v>
       </c>
       <c r="I47" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="J47" t="n">
         <v>3.35</v>
@@ -9517,10 +9517,10 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="G48" t="n">
         <v>1.5</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G49" t="n">
         <v>2.7</v>
@@ -9890,7 +9890,7 @@
         <v>3.15</v>
       </c>
       <c r="K49" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q49" t="n">
         <v>2.26</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
         <v>3.4</v>
       </c>
       <c r="K50" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -10278,7 +10278,7 @@
         <v>4.1</v>
       </c>
       <c r="K51" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -10529,7 +10529,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD52" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AE52" t="n">
         <v>17.5</v>
@@ -10574,7 +10574,7 @@
         <v>10.5</v>
       </c>
       <c r="AS52" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AT52" t="n">
         <v>17.5</v>
@@ -10589,7 +10589,7 @@
         <v>15.5</v>
       </c>
       <c r="AX52" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AY52" t="n">
         <v>17</v>
@@ -10598,7 +10598,7 @@
         <v>16.5</v>
       </c>
       <c r="BA52" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB52" t="n">
         <v>46</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -10654,13 +10654,13 @@
         <v>2.26</v>
       </c>
       <c r="G53" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H53" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I53" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J53" t="n">
         <v>3.5</v>
@@ -10705,7 +10705,7 @@
         <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y53" t="n">
         <v>13.5</v>
@@ -10807,14 +10807,14 @@
         <v>65</v>
       </c>
       <c r="BF53" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BG53" t="n">
         <v>42</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -10854,7 +10854,7 @@
         <v>3.85</v>
       </c>
       <c r="I54" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J54" t="n">
         <v>3.1</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
         <v>2.16</v>
       </c>
       <c r="G55" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H55" t="n">
         <v>3.45</v>
@@ -11051,7 +11051,7 @@
         <v>3.85</v>
       </c>
       <c r="J55" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K55" t="n">
         <v>3.8</v>
@@ -11069,10 +11069,10 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -11260,16 +11260,16 @@
         <v>3.5</v>
       </c>
       <c r="O56" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P56" t="n">
         <v>1.83</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R56" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S56" t="n">
         <v>3.85</v>
@@ -11278,7 +11278,7 @@
         <v>1.83</v>
       </c>
       <c r="U56" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
@@ -11299,28 +11299,28 @@
         <v>55</v>
       </c>
       <c r="AB56" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC56" t="n">
         <v>7.6</v>
       </c>
       <c r="AD56" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE56" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF56" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG56" t="n">
         <v>12</v>
       </c>
       <c r="AH56" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI56" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ56" t="n">
         <v>38</v>
@@ -11329,28 +11329,28 @@
         <v>30</v>
       </c>
       <c r="AL56" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM56" t="n">
         <v>1000</v>
       </c>
       <c r="AN56" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO56" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP56" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ56" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR56" t="n">
         <v>18</v>
       </c>
       <c r="AS56" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="AT56" t="n">
         <v>9</v>
@@ -11359,13 +11359,13 @@
         <v>6.8</v>
       </c>
       <c r="AV56" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW56" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AX56" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY56" t="n">
         <v>10.5</v>
@@ -11377,26 +11377,26 @@
         <v>40</v>
       </c>
       <c r="BB56" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BC56" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BD56" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="BE56" t="n">
         <v>38</v>
       </c>
       <c r="BF56" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BG56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
         <v>2.08</v>
       </c>
       <c r="G57" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H57" t="n">
         <v>3.85</v>
@@ -11457,10 +11457,10 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -11651,10 +11651,10 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -11821,13 +11821,13 @@
         <v>6.2</v>
       </c>
       <c r="H59" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="I59" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="J59" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K59" t="n">
         <v>4.1</v>
@@ -11848,7 +11848,7 @@
         <v>1.85</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
         <v>2.16</v>
       </c>
       <c r="I60" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J60" t="n">
         <v>4.2</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G61" t="n">
         <v>1.67</v>
@@ -12218,7 +12218,7 @@
         <v>4.1</v>
       </c>
       <c r="K61" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -12233,7 +12233,7 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Q61" t="n">
         <v>1.62</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -12400,16 +12400,16 @@
         <v>1.69</v>
       </c>
       <c r="G62" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="H62" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I62" t="n">
         <v>7.4</v>
       </c>
       <c r="J62" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K62" t="n">
         <v>4.2</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -12788,19 +12788,19 @@
         <v>2.44</v>
       </c>
       <c r="G64" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="H64" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I64" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="J64" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="K64" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -12815,10 +12815,10 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -14343,7 +14343,7 @@
         <v>3.35</v>
       </c>
       <c r="H72" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="I72" t="n">
         <v>3.2</v>
@@ -14352,7 +14352,7 @@
         <v>3.25</v>
       </c>
       <c r="K72" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -14749,13 +14749,13 @@
         <v>1.06</v>
       </c>
       <c r="N74" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O74" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P74" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q74" t="n">
         <v>1.85</v>
@@ -14767,10 +14767,10 @@
         <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U74" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
@@ -14779,10 +14779,10 @@
         <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y74" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z74" t="n">
         <v>85</v>
@@ -14791,10 +14791,10 @@
         <v>1000</v>
       </c>
       <c r="AB74" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC74" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD74" t="n">
         <v>36</v>
@@ -14803,22 +14803,22 @@
         <v>190</v>
       </c>
       <c r="AF74" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AG74" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH74" t="n">
         <v>28</v>
       </c>
       <c r="AI74" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AJ74" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK74" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL74" t="n">
         <v>42</v>
@@ -14827,49 +14827,49 @@
         <v>200</v>
       </c>
       <c r="AN74" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AO74" t="n">
         <v>270</v>
       </c>
       <c r="AP74" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ74" t="n">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="AR74" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="AS74" t="n">
-        <v>8.6</v>
+        <v>95</v>
       </c>
       <c r="AT74" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU74" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV74" t="n">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="AW74" t="n">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="AX74" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AY74" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ74" t="n">
-        <v>6.8</v>
+        <v>19</v>
       </c>
       <c r="BA74" t="n">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="BB74" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC74" t="n">
         <v>13.5</v>
@@ -14878,17 +14878,17 @@
         <v>32</v>
       </c>
       <c r="BE74" t="n">
-        <v>8.4</v>
+        <v>46</v>
       </c>
       <c r="BF74" t="n">
         <v>6.2</v>
       </c>
       <c r="BG74" t="n">
-        <v>8.6</v>
+        <v>48</v>
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -15310,19 +15310,19 @@
         <v>2.52</v>
       </c>
       <c r="G77" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="H77" t="n">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="I77" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="J77" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K77" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -15516,7 +15516,7 @@
         <v>4.2</v>
       </c>
       <c r="K78" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -15531,7 +15531,7 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q78" t="n">
         <v>1.46</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -15695,13 +15695,13 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G79" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H79" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I79" t="n">
         <v>3.25</v>
@@ -15710,7 +15710,7 @@
         <v>2.98</v>
       </c>
       <c r="K79" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q79" t="n">
         <v>1.87</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -15889,19 +15889,19 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G80" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H80" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I80" t="n">
         <v>3.45</v>
       </c>
       <c r="J80" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K80" t="n">
         <v>3.65</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -16092,13 +16092,13 @@
         <v>10</v>
       </c>
       <c r="I81" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J81" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K81" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -16107,7 +16107,7 @@
         <v>1.01</v>
       </c>
       <c r="N81" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="O81" t="n">
         <v>1.11</v>
@@ -16125,7 +16125,7 @@
         <v>1.85</v>
       </c>
       <c r="T81" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U81" t="n">
         <v>2.36</v>
@@ -16167,7 +16167,7 @@
         <v>11.5</v>
       </c>
       <c r="AH81" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI81" t="n">
         <v>85</v>
@@ -16179,7 +16179,7 @@
         <v>13.5</v>
       </c>
       <c r="AL81" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM81" t="n">
         <v>80</v>
@@ -16224,7 +16224,7 @@
         <v>19.5</v>
       </c>
       <c r="BA81" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="BB81" t="n">
         <v>11</v>
@@ -16242,11 +16242,11 @@
         <v>3.1</v>
       </c>
       <c r="BG81" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -16280,10 +16280,10 @@
         <v>1.69</v>
       </c>
       <c r="G82" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H82" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I82" t="n">
         <v>5.4</v>
@@ -16292,7 +16292,7 @@
         <v>4.4</v>
       </c>
       <c r="K82" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -16334,7 +16334,7 @@
         <v>28</v>
       </c>
       <c r="Y82" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z82" t="n">
         <v>50</v>
@@ -16343,7 +16343,7 @@
         <v>1000</v>
       </c>
       <c r="AB82" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC82" t="n">
         <v>10.5</v>
@@ -16367,7 +16367,7 @@
         <v>55</v>
       </c>
       <c r="AJ82" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK82" t="n">
         <v>16.5</v>
@@ -16382,13 +16382,13 @@
         <v>6.8</v>
       </c>
       <c r="AO82" t="n">
-        <v>46</v>
+        <v>190</v>
       </c>
       <c r="AP82" t="n">
         <v>22</v>
       </c>
       <c r="AQ82" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AR82" t="n">
         <v>40</v>
@@ -16427,7 +16427,7 @@
         <v>14</v>
       </c>
       <c r="BD82" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE82" t="n">
         <v>55</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -16501,16 +16501,16 @@
         <v>1.18</v>
       </c>
       <c r="P83" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="Q83" t="n">
         <v>1.54</v>
       </c>
       <c r="R83" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="S83" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="T83" t="n">
         <v>1.84</v>
@@ -16525,7 +16525,7 @@
         <v>0</v>
       </c>
       <c r="X83" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y83" t="n">
         <v>11.5</v>
@@ -16537,10 +16537,10 @@
         <v>12</v>
       </c>
       <c r="AB83" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AC83" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD83" t="n">
         <v>10.5</v>
@@ -16549,16 +16549,16 @@
         <v>14</v>
       </c>
       <c r="AF83" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AG83" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AH83" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI83" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ83" t="n">
         <v>1000</v>
@@ -16567,19 +16567,19 @@
         <v>150</v>
       </c>
       <c r="AL83" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM83" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN83" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AO83" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AP83" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="AQ83" t="n">
         <v>10</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -16671,7 +16671,7 @@
         <v>4.1</v>
       </c>
       <c r="H84" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I84" t="n">
         <v>1.91</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -17062,7 +17062,7 @@
         <v>5.4</v>
       </c>
       <c r="I86" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="J86" t="n">
         <v>3.55</v>
@@ -17083,10 +17083,10 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="R86" t="n">
         <v>0</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -17635,22 +17635,22 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="G89" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="H89" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="I89" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J89" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K89" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -17668,7 +17668,7 @@
         <v>2.08</v>
       </c>
       <c r="Q89" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -17829,16 +17829,16 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="G90" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="H90" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="I90" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="J90" t="n">
         <v>4.6</v>
@@ -17859,7 +17859,7 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q90" t="n">
         <v>1.68</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -18023,22 +18023,22 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G91" t="n">
         <v>2.46</v>
       </c>
       <c r="H91" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I91" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J91" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K91" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -18220,7 +18220,7 @@
         <v>1.36</v>
       </c>
       <c r="G92" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="H92" t="n">
         <v>10</v>
@@ -18229,10 +18229,10 @@
         <v>12</v>
       </c>
       <c r="J92" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K92" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -18247,10 +18247,10 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -18993,7 +18993,7 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G96" t="n">
         <v>3.5</v>
@@ -19008,7 +19008,7 @@
         <v>3.45</v>
       </c>
       <c r="K96" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -19193,16 +19193,16 @@
         <v>1.76</v>
       </c>
       <c r="H97" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I97" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J97" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K97" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -19217,10 +19217,10 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="Q97" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="R97" t="n">
         <v>0</v>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -19381,22 +19381,22 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G98" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="H98" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I98" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="J98" t="n">
         <v>4.2</v>
       </c>
       <c r="K98" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -19605,7 +19605,7 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Q99" t="n">
         <v>2.2</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -19781,7 +19781,7 @@
         <v>3.4</v>
       </c>
       <c r="J100" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="K100" t="n">
         <v>2.96</v>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -19972,7 +19972,7 @@
         <v>2.5</v>
       </c>
       <c r="I101" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="J101" t="n">
         <v>2.88</v>
@@ -19993,10 +19993,10 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q101" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -20554,10 +20554,10 @@
         <v>2.76</v>
       </c>
       <c r="I104" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="J104" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="K104" t="n">
         <v>3.6</v>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -20745,7 +20745,7 @@
         <v>2.88</v>
       </c>
       <c r="H105" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I105" t="n">
         <v>2.66</v>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -21484,7 +21484,7 @@
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -21678,7 +21678,7 @@
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G110" t="n">
         <v>3.35</v>
@@ -21730,7 +21730,7 @@
         <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N110" t="n">
         <v>4.1</v>
@@ -21739,7 +21739,7 @@
         <v>1.29</v>
       </c>
       <c r="P110" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q110" t="n">
         <v>1.87</v>
@@ -21814,7 +21814,7 @@
         <v>34</v>
       </c>
       <c r="AO110" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AP110" t="n">
         <v>14</v>
@@ -21826,7 +21826,7 @@
         <v>14.5</v>
       </c>
       <c r="AS110" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AT110" t="n">
         <v>12.5</v>
@@ -21853,7 +21853,7 @@
         <v>30</v>
       </c>
       <c r="BB110" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BC110" t="n">
         <v>30</v>
@@ -21865,14 +21865,14 @@
         <v>34</v>
       </c>
       <c r="BF110" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="BG110" t="n">
         <v>16</v>
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -21903,7 +21903,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="G111" t="n">
         <v>2.06</v>
@@ -21912,7 +21912,7 @@
         <v>4</v>
       </c>
       <c r="I111" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J111" t="n">
         <v>3.55</v>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -22112,7 +22112,7 @@
         <v>3.3</v>
       </c>
       <c r="K112" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -22127,7 +22127,7 @@
         <v>1.39</v>
       </c>
       <c r="P112" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q112" t="n">
         <v>2.22</v>
@@ -22142,7 +22142,7 @@
         <v>1.9</v>
       </c>
       <c r="U112" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V112" t="n">
         <v>0</v>
@@ -22232,7 +22232,7 @@
         <v>18</v>
       </c>
       <c r="AY112" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ112" t="n">
         <v>18</v>
@@ -22250,7 +22250,7 @@
         <v>30</v>
       </c>
       <c r="BE112" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BF112" t="n">
         <v>28</v>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -22485,22 +22485,22 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="G114" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="H114" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="I114" t="n">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="J114" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="K114" t="n">
-        <v>5.4</v>
+        <v>3.55</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -22515,10 +22515,10 @@
         <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Q114" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
@@ -22648,7 +22648,7 @@
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -22842,7 +22842,7 @@
       </c>
       <c r="BH115" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -22876,10 +22876,10 @@
         <v>5.4</v>
       </c>
       <c r="G116" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H116" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="I116" t="n">
         <v>1.66</v>
@@ -22888,7 +22888,7 @@
         <v>4.5</v>
       </c>
       <c r="K116" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -23036,7 +23036,7 @@
       </c>
       <c r="BH116" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -23070,7 +23070,7 @@
         <v>1.42</v>
       </c>
       <c r="G117" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H117" t="n">
         <v>8.800000000000001</v>
@@ -23079,10 +23079,10 @@
         <v>9.6</v>
       </c>
       <c r="J117" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K117" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -23112,7 +23112,7 @@
         <v>1.96</v>
       </c>
       <c r="U117" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V117" t="n">
         <v>0</v>
@@ -23230,7 +23230,7 @@
       </c>
       <c r="BH117" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -23291,10 +23291,10 @@
         <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="Q118" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R118" t="n">
         <v>0</v>
@@ -23424,7 +23424,7 @@
       </c>
       <c r="BH118" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -23464,13 +23464,13 @@
         <v>4.1</v>
       </c>
       <c r="I119" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J119" t="n">
         <v>2.76</v>
       </c>
       <c r="K119" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -23618,7 +23618,7 @@
       </c>
       <c r="BH119" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -23812,7 +23812,7 @@
       </c>
       <c r="BH120" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -23843,22 +23843,22 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G121" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="H121" t="n">
         <v>2.84</v>
       </c>
       <c r="I121" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="J121" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="K121" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -24006,7 +24006,7 @@
       </c>
       <c r="BH121" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -24037,7 +24037,7 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G122" t="n">
         <v>2.48</v>
@@ -24046,13 +24046,13 @@
         <v>3.55</v>
       </c>
       <c r="I122" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="J122" t="n">
         <v>3.2</v>
       </c>
       <c r="K122" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -24067,10 +24067,10 @@
         <v>0</v>
       </c>
       <c r="P122" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q122" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="R122" t="n">
         <v>0</v>
@@ -24200,7 +24200,7 @@
       </c>
       <c r="BH122" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -24231,22 +24231,22 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="G123" t="n">
         <v>4.8</v>
       </c>
       <c r="H123" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I123" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="J123" t="n">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="K123" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -24261,7 +24261,7 @@
         <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Q123" t="n">
         <v>2.28</v>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="BH123" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -24588,7 +24588,7 @@
       </c>
       <c r="BH124" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -24622,13 +24622,13 @@
         <v>2.26</v>
       </c>
       <c r="G125" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H125" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I125" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J125" t="n">
         <v>3.05</v>
@@ -24782,7 +24782,7 @@
       </c>
       <c r="BH125" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -24846,7 +24846,7 @@
         <v>2</v>
       </c>
       <c r="Q126" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R126" t="n">
         <v>0</v>
@@ -24867,7 +24867,7 @@
         <v>0</v>
       </c>
       <c r="X126" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Y126" t="n">
         <v>15</v>
@@ -24879,10 +24879,10 @@
         <v>55</v>
       </c>
       <c r="AB126" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC126" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD126" t="n">
         <v>15.5</v>
@@ -24894,7 +24894,7 @@
         <v>22</v>
       </c>
       <c r="AG126" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH126" t="n">
         <v>20</v>
@@ -24927,10 +24927,10 @@
         <v>11</v>
       </c>
       <c r="AR126" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AS126" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AT126" t="n">
         <v>10</v>
@@ -24939,10 +24939,10 @@
         <v>7.2</v>
       </c>
       <c r="AV126" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AW126" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AX126" t="n">
         <v>13</v>
@@ -24951,32 +24951,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ126" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BA126" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BB126" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BC126" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BD126" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE126" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF126" t="n">
         <v>15.5</v>
       </c>
       <c r="BG126" t="n">
-        <v>3.85</v>
+        <v>19</v>
       </c>
       <c r="BH126" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -25010,16 +25010,16 @@
         <v>2.5</v>
       </c>
       <c r="G127" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="H127" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I127" t="n">
         <v>3.1</v>
       </c>
       <c r="J127" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K127" t="n">
         <v>3.8</v>
@@ -25082,7 +25082,7 @@
         <v>15</v>
       </c>
       <c r="AE127" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF127" t="n">
         <v>21</v>
@@ -25091,13 +25091,13 @@
         <v>14</v>
       </c>
       <c r="AH127" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI127" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ127" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK127" t="n">
         <v>32</v>
@@ -25109,10 +25109,10 @@
         <v>1000</v>
       </c>
       <c r="AN127" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO127" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AP127" t="n">
         <v>13.5</v>
@@ -25124,7 +25124,7 @@
         <v>15.5</v>
       </c>
       <c r="AS127" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT127" t="n">
         <v>9</v>
@@ -25136,7 +25136,7 @@
         <v>10</v>
       </c>
       <c r="AW127" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX127" t="n">
         <v>13.5</v>
@@ -25148,19 +25148,19 @@
         <v>12.5</v>
       </c>
       <c r="BA127" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB127" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BC127" t="n">
         <v>20</v>
       </c>
       <c r="BD127" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BE127" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF127" t="n">
         <v>16</v>
@@ -25170,7 +25170,7 @@
       </c>
       <c r="BH127" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -25364,7 +25364,7 @@
       </c>
       <c r="BH128" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -25401,13 +25401,13 @@
         <v>3.45</v>
       </c>
       <c r="H129" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I129" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="J129" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K129" t="n">
         <v>3.35</v>
@@ -25558,7 +25558,7 @@
       </c>
       <c r="BH129" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-11.xlsx
@@ -790,7 +790,7 @@
         <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="R2" t="n">
         <v>1.34</v>
@@ -799,7 +799,7 @@
         <v>2.74</v>
       </c>
       <c r="T2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U2" t="n">
         <v>2.16</v>
@@ -811,10 +811,10 @@
         <v>1.97</v>
       </c>
       <c r="X2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y2" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z2" t="n">
         <v>38</v>
@@ -823,7 +823,7 @@
         <v>110</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC2" t="n">
         <v>9.800000000000001</v>
@@ -868,59 +868,59 @@
         <v>14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV2" t="n">
         <v>15</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AX2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
         <v>15</v>
       </c>
       <c r="BA2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE2" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>5</v>
       </c>
       <c r="BF2" t="n">
         <v>9.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.23</v>
@@ -984,13 +984,13 @@
         <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="R3" t="n">
         <v>1.48</v>
       </c>
       <c r="S3" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="T3" t="n">
         <v>1.61</v>
@@ -1014,7 +1014,7 @@
         <v>26</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB3" t="n">
         <v>13</v>
@@ -1041,7 +1041,7 @@
         <v>42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK3" t="n">
         <v>22</v>
@@ -1056,10 +1056,10 @@
         <v>13.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>14</v>
@@ -1068,7 +1068,7 @@
         <v>22</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT3" t="n">
         <v>11</v>
@@ -1101,7 +1101,7 @@
         <v>18.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE3" t="n">
         <v>55</v>
@@ -1110,11 +1110,11 @@
         <v>11.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G4" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="H4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I4" t="n">
         <v>3.1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.25</v>
       </c>
       <c r="J4" t="n">
         <v>4.4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.19</v>
@@ -1169,19 +1169,19 @@
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P4" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S4" t="n">
         <v>1.79</v>
@@ -1193,13 +1193,13 @@
         <v>3.4</v>
       </c>
       <c r="V4" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W4" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="X4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Y4" t="n">
         <v>32</v>
@@ -1211,7 +1211,7 @@
         <v>55</v>
       </c>
       <c r="AB4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC4" t="n">
         <v>13.5</v>
@@ -1235,7 +1235,7 @@
         <v>27</v>
       </c>
       <c r="AJ4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK4" t="n">
         <v>21</v>
@@ -1247,13 +1247,13 @@
         <v>36</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AO4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="AQ4" t="n">
         <v>26</v>
@@ -1274,7 +1274,7 @@
         <v>13.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX4" t="n">
         <v>21</v>
@@ -1301,14 +1301,14 @@
         <v>29</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG4" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1342,10 @@
         <v>2.54</v>
       </c>
       <c r="G5" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H5" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I5" t="n">
         <v>2.7</v>
@@ -1357,7 +1357,7 @@
         <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="M5" t="n">
         <v>1.04</v>
@@ -1366,19 +1366,19 @@
         <v>5.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P5" t="n">
         <v>2.48</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="R5" t="n">
         <v>1.61</v>
       </c>
       <c r="S5" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="T5" t="n">
         <v>1.54</v>
@@ -1393,7 +1393,7 @@
         <v>1.58</v>
       </c>
       <c r="X5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y5" t="n">
         <v>18.5</v>
@@ -1402,7 +1402,7 @@
         <v>24</v>
       </c>
       <c r="AA5" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AB5" t="n">
         <v>18</v>
@@ -1426,7 +1426,7 @@
         <v>17</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ5" t="n">
         <v>44</v>
@@ -1447,10 +1447,10 @@
         <v>17</v>
       </c>
       <c r="AP5" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR5" t="n">
         <v>18.5</v>
@@ -1474,16 +1474,16 @@
         <v>17.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ5" t="n">
         <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>21</v>
+        <v>4.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
@@ -1492,17 +1492,17 @@
         <v>20</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BF5" t="n">
         <v>12.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T6" t="n">
         <v>1.01</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="G7" t="n">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X7" t="n">
         <v>1000</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K7" t="n">
-        <v>950</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G8" t="n">
         <v>2.46</v>
       </c>
       <c r="H8" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I8" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K8" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1954,7 +1954,7 @@
         <v>1.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.48</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G11" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H11" t="n">
         <v>3.45</v>
@@ -2515,7 +2515,7 @@
         <v>3.7</v>
       </c>
       <c r="J11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K11" t="n">
         <v>3.95</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G13" t="n">
         <v>1.46</v>
       </c>
       <c r="H13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I13" t="n">
         <v>10.5</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="G15" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="H15" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K15" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G16" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="H16" t="n">
         <v>5.6</v>
       </c>
       <c r="I16" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J16" t="n">
         <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3506,7 +3506,7 @@
         <v>2.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J17" t="n">
         <v>5</v>
@@ -3733,7 +3733,7 @@
         <v>240</v>
       </c>
       <c r="AB17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC17" t="n">
         <v>10.5</v>
@@ -3742,13 +3742,13 @@
         <v>30</v>
       </c>
       <c r="AE17" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF17" t="n">
         <v>9.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH17" t="n">
         <v>23</v>
@@ -3769,7 +3769,7 @@
         <v>110</v>
       </c>
       <c r="AN17" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AO17" t="n">
         <v>150</v>
@@ -3778,7 +3778,7 @@
         <v>20</v>
       </c>
       <c r="AQ17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR17" t="n">
         <v>55</v>
@@ -3796,7 +3796,7 @@
         <v>27</v>
       </c>
       <c r="AW17" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="AX17" t="n">
         <v>9</v>
@@ -3811,7 +3811,7 @@
         <v>75</v>
       </c>
       <c r="BB17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC17" t="n">
         <v>13.5</v>
@@ -3820,7 +3820,7 @@
         <v>27</v>
       </c>
       <c r="BE17" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BF17" t="n">
         <v>5.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
         <v>2.62</v>
       </c>
       <c r="H18" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I18" t="n">
         <v>3.05</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -4061,13 +4061,13 @@
         <v>2.24</v>
       </c>
       <c r="H19" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I19" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J19" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K19" t="n">
         <v>4.1</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="G20" t="n">
         <v>1.91</v>
@@ -4279,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="Q20" t="n">
         <v>1.52</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -4446,10 +4446,10 @@
         <v>3.45</v>
       </c>
       <c r="G21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H21" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="I21" t="n">
         <v>2.46</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q22" t="n">
         <v>2.6</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G23" t="n">
         <v>1.82</v>
@@ -4840,7 +4840,7 @@
         <v>5.2</v>
       </c>
       <c r="I23" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J23" t="n">
         <v>3.85</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G24" t="n">
         <v>1.88</v>
@@ -5034,7 +5034,7 @@
         <v>4.8</v>
       </c>
       <c r="I24" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J24" t="n">
         <v>3.75</v>
@@ -5058,7 +5058,7 @@
         <v>1.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>1.55</v>
       </c>
       <c r="G30" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="H30" t="n">
         <v>4.8</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="G31" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H31" t="n">
         <v>3.25</v>
@@ -6413,25 +6413,25 @@
         <v>1.45</v>
       </c>
       <c r="P31" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S31" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="T31" t="n">
         <v>1.93</v>
       </c>
       <c r="U31" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V31" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W31" t="n">
         <v>1.62</v>
@@ -6440,28 +6440,28 @@
         <v>11.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD31" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF31" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG31" t="n">
         <v>14.5</v>
@@ -6470,13 +6470,13 @@
         <v>23</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ31" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK31" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL31" t="n">
         <v>1000</v>
@@ -6485,7 +6485,7 @@
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
@@ -6500,7 +6500,7 @@
         <v>18</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT31" t="n">
         <v>7</v>
@@ -6512,7 +6512,7 @@
         <v>11.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>5.7</v>
+        <v>36</v>
       </c>
       <c r="AX31" t="n">
         <v>11.5</v>
@@ -6521,32 +6521,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.9</v>
+        <v>15</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB31" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.8</v>
+        <v>40</v>
       </c>
       <c r="BE31" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BF31" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -6583,16 +6583,16 @@
         <v>3.8</v>
       </c>
       <c r="H32" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="I32" t="n">
         <v>3.35</v>
       </c>
       <c r="J32" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K32" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -6610,7 +6610,7 @@
         <v>1.71</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G35" t="n">
         <v>6.4</v>
@@ -7168,13 +7168,13 @@
         <v>1.71</v>
       </c>
       <c r="I35" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="J35" t="n">
         <v>3.8</v>
       </c>
       <c r="K35" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G36" t="n">
         <v>2.26</v>
@@ -7494,7 +7494,7 @@
         <v>18.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BB36" t="n">
         <v>23</v>
@@ -7503,7 +7503,7 @@
         <v>18.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="BE36" t="n">
         <v>44</v>
@@ -7512,11 +7512,11 @@
         <v>16.5</v>
       </c>
       <c r="BG36" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -7577,10 +7577,10 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -7977,7 +7977,7 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U39" t="n">
         <v>1.79</v>
@@ -8013,7 +8013,7 @@
         <v>85</v>
       </c>
       <c r="AF39" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG39" t="n">
         <v>11</v>
@@ -8055,7 +8055,7 @@
         <v>40</v>
       </c>
       <c r="AT39" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU39" t="n">
         <v>7.2</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -8132,19 +8132,19 @@
         <v>2.98</v>
       </c>
       <c r="G40" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="H40" t="n">
         <v>2.46</v>
       </c>
       <c r="I40" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="J40" t="n">
         <v>3</v>
       </c>
       <c r="K40" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -8159,7 +8159,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q40" t="n">
         <v>2.24</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
         <v>1.7</v>
       </c>
       <c r="I41" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="J41" t="n">
         <v>3.5</v>
@@ -8356,7 +8356,7 @@
         <v>1.99</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
         <v>1.38</v>
       </c>
       <c r="S42" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T42" t="n">
         <v>1.76</v>
@@ -8586,7 +8586,7 @@
         <v>13</v>
       </c>
       <c r="AC42" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD42" t="n">
         <v>11.5</v>
@@ -8610,7 +8610,7 @@
         <v>55</v>
       </c>
       <c r="AK42" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL42" t="n">
         <v>46</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -8717,7 +8717,7 @@
         <v>1.57</v>
       </c>
       <c r="H43" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I43" t="n">
         <v>6.4</v>
@@ -8738,7 +8738,7 @@
         <v>6.4</v>
       </c>
       <c r="O43" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P43" t="n">
         <v>2.8</v>
@@ -8753,7 +8753,7 @@
         <v>2.24</v>
       </c>
       <c r="T43" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U43" t="n">
         <v>2.4</v>
@@ -8777,13 +8777,13 @@
         <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC43" t="n">
         <v>12</v>
       </c>
       <c r="AD43" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE43" t="n">
         <v>85</v>
@@ -8798,7 +8798,7 @@
         <v>18.5</v>
       </c>
       <c r="AI43" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ43" t="n">
         <v>15.5</v>
@@ -8819,10 +8819,10 @@
         <v>55</v>
       </c>
       <c r="AP43" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AQ43" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="AR43" t="n">
         <v>29</v>
@@ -8831,7 +8831,7 @@
         <v>44</v>
       </c>
       <c r="AT43" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU43" t="n">
         <v>10.5</v>
@@ -8849,7 +8849,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ43" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA43" t="n">
         <v>29</v>
@@ -8861,20 +8861,20 @@
         <v>13</v>
       </c>
       <c r="BD43" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="BE43" t="n">
         <v>32</v>
       </c>
       <c r="BF43" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BG43" t="n">
         <v>29</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -8950,7 +8950,7 @@
         <v>1.57</v>
       </c>
       <c r="U44" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -8977,7 +8977,7 @@
         <v>9</v>
       </c>
       <c r="AD44" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE44" t="n">
         <v>26</v>
@@ -9046,7 +9046,7 @@
         <v>13</v>
       </c>
       <c r="BA44" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BB44" t="n">
         <v>32</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -9102,10 +9102,10 @@
         <v>2.02</v>
       </c>
       <c r="G45" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H45" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I45" t="n">
         <v>3.8</v>
@@ -9144,7 +9144,7 @@
         <v>1.53</v>
       </c>
       <c r="U45" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -9207,13 +9207,13 @@
         <v>25</v>
       </c>
       <c r="AP45" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ45" t="n">
         <v>18.5</v>
       </c>
       <c r="AR45" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS45" t="n">
         <v>50</v>
@@ -9225,7 +9225,7 @@
         <v>9</v>
       </c>
       <c r="AV45" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW45" t="n">
         <v>22</v>
@@ -9249,20 +9249,20 @@
         <v>16.5</v>
       </c>
       <c r="BD45" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BE45" t="n">
         <v>28</v>
       </c>
       <c r="BF45" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BG45" t="n">
         <v>21</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -9293,22 +9293,22 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="G46" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="H46" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="I46" t="n">
         <v>2.86</v>
       </c>
       <c r="J46" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="K46" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -9323,10 +9323,10 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="G47" t="n">
         <v>3.15</v>
@@ -9496,7 +9496,7 @@
         <v>2.52</v>
       </c>
       <c r="I47" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="J47" t="n">
         <v>3.35</v>
@@ -9517,10 +9517,10 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9693,7 @@
         <v>1000</v>
       </c>
       <c r="J48" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K48" t="n">
         <v>950</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -10263,10 +10263,10 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="G51" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="H51" t="n">
         <v>4.5</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -10490,7 +10490,7 @@
         <v>2.18</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R52" t="n">
         <v>1.45</v>
@@ -10568,7 +10568,7 @@
         <v>16</v>
       </c>
       <c r="AQ52" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR52" t="n">
         <v>10.5</v>
@@ -10589,7 +10589,7 @@
         <v>15.5</v>
       </c>
       <c r="AX52" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY52" t="n">
         <v>17</v>
@@ -10604,10 +10604,10 @@
         <v>46</v>
       </c>
       <c r="BC52" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BD52" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="BE52" t="n">
         <v>55</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
         <v>1.34</v>
       </c>
       <c r="P53" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q53" t="n">
         <v>2.04</v>
@@ -10771,7 +10771,7 @@
         <v>50</v>
       </c>
       <c r="AT53" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU53" t="n">
         <v>7.2</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
         <v>1.03</v>
       </c>
       <c r="K54" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -11054,7 +11054,7 @@
         <v>3.1</v>
       </c>
       <c r="K55" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -11263,10 +11263,10 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -11430,10 +11430,10 @@
         <v>2.54</v>
       </c>
       <c r="G57" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H57" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I57" t="n">
         <v>3.2</v>
@@ -11472,7 +11472,7 @@
         <v>1.83</v>
       </c>
       <c r="U57" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V57" t="n">
         <v>0</v>
@@ -11529,13 +11529,13 @@
         <v>1000</v>
       </c>
       <c r="AN57" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO57" t="n">
         <v>38</v>
       </c>
       <c r="AP57" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ57" t="n">
         <v>10.5</v>
@@ -11571,7 +11571,7 @@
         <v>28</v>
       </c>
       <c r="BB57" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BC57" t="n">
         <v>19</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -11651,10 +11651,10 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
         <v>3.9</v>
       </c>
       <c r="I59" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="J59" t="n">
         <v>3.05</v>
@@ -11845,7 +11845,7 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q59" t="n">
         <v>2.58</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -12203,16 +12203,16 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G61" t="n">
         <v>3.15</v>
       </c>
       <c r="H61" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I61" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="J61" t="n">
         <v>4.2</v>
@@ -12233,7 +12233,7 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q61" t="n">
         <v>1.35</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G62" t="n">
         <v>1.67</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -12591,10 +12591,10 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G63" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="H63" t="n">
         <v>5.4</v>
@@ -12603,7 +12603,7 @@
         <v>7.4</v>
       </c>
       <c r="J63" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="K63" t="n">
         <v>4.2</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -12785,22 +12785,22 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="G64" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H64" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="I64" t="n">
         <v>4.2</v>
       </c>
       <c r="J64" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="K64" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -12815,7 +12815,7 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="Q64" t="n">
         <v>2.3</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -12979,22 +12979,22 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G65" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="H65" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I65" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J65" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="K65" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -13009,7 +13009,7 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q65" t="n">
         <v>2.48</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -13176,13 +13176,13 @@
         <v>2.5</v>
       </c>
       <c r="G66" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="H66" t="n">
         <v>2.86</v>
       </c>
       <c r="I66" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="J66" t="n">
         <v>3.4</v>
@@ -13203,11 +13203,11 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q66" t="n">
         <v>1.94</v>
       </c>
-      <c r="Q66" t="n">
-        <v>1.93</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -13370,13 +13370,13 @@
         <v>2.64</v>
       </c>
       <c r="G67" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="H67" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I67" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="J67" t="n">
         <v>3.2</v>
@@ -13397,10 +13397,10 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -13570,10 +13570,10 @@
         <v>1.86</v>
       </c>
       <c r="I68" t="n">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="J68" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K68" t="n">
         <v>7</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -14143,7 +14143,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G71" t="n">
         <v>2.98</v>
@@ -14158,7 +14158,7 @@
         <v>3.15</v>
       </c>
       <c r="K71" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -14176,7 +14176,7 @@
         <v>1.81</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -14531,7 +14531,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G73" t="n">
         <v>3.35</v>
@@ -14546,7 +14546,7 @@
         <v>3.25</v>
       </c>
       <c r="K73" t="n">
-        <v>6.6</v>
+        <v>950</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -14564,7 +14564,7 @@
         <v>2.04</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -14725,22 +14725,22 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="G74" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="H74" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="I74" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="J74" t="n">
         <v>4.2</v>
       </c>
       <c r="K74" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -14755,7 +14755,7 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="Q74" t="n">
         <v>1.46</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -14919,13 +14919,13 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G75" t="n">
         <v>2.76</v>
       </c>
       <c r="H75" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="I75" t="n">
         <v>2.94</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -15116,16 +15116,16 @@
         <v>5.3</v>
       </c>
       <c r="G76" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="H76" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="I76" t="n">
         <v>1.68</v>
       </c>
       <c r="J76" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K76" t="n">
         <v>5</v>
@@ -15143,10 +15143,10 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -15322,7 +15322,7 @@
         <v>1.03</v>
       </c>
       <c r="K77" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -15501,10 +15501,10 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G78" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H78" t="n">
         <v>9</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U78" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -15627,7 +15627,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV78" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW78" t="n">
         <v>42</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -15695,19 +15695,19 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G79" t="n">
         <v>2.32</v>
       </c>
       <c r="H79" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I79" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="J79" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K79" t="n">
         <v>4.1</v>
@@ -15725,7 +15725,7 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q79" t="n">
         <v>1.73</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -16098,7 +16098,7 @@
         <v>3.2</v>
       </c>
       <c r="K81" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -16280,7 +16280,7 @@
         <v>2.34</v>
       </c>
       <c r="G82" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H82" t="n">
         <v>3.15</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -16480,13 +16480,13 @@
         <v>10</v>
       </c>
       <c r="I83" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J83" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K83" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -16501,10 +16501,10 @@
         <v>1.11</v>
       </c>
       <c r="P83" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="R83" t="n">
         <v>2.08</v>
@@ -16516,7 +16516,7 @@
         <v>1.67</v>
       </c>
       <c r="U83" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -16528,10 +16528,10 @@
         <v>48</v>
       </c>
       <c r="Y83" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Z83" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA83" t="n">
         <v>1000</v>
@@ -16543,10 +16543,10 @@
         <v>17</v>
       </c>
       <c r="AD83" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AE83" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF83" t="n">
         <v>12.5</v>
@@ -16558,34 +16558,34 @@
         <v>23</v>
       </c>
       <c r="AI83" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ83" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AK83" t="n">
         <v>13.5</v>
       </c>
       <c r="AL83" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM83" t="n">
         <v>80</v>
       </c>
       <c r="AN83" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AO83" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP83" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AQ83" t="n">
         <v>27</v>
       </c>
       <c r="AR83" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AS83" t="n">
         <v>95</v>
@@ -16609,7 +16609,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ83" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA83" t="n">
         <v>34</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -16665,10 +16665,10 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G84" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H84" t="n">
         <v>5.3</v>
@@ -16677,10 +16677,10 @@
         <v>5.4</v>
       </c>
       <c r="J84" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K84" t="n">
         <v>4.5</v>
-      </c>
-      <c r="K84" t="n">
-        <v>4.6</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -16698,7 +16698,7 @@
         <v>2.66</v>
       </c>
       <c r="Q84" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R84" t="n">
         <v>1.65</v>
@@ -16710,7 +16710,7 @@
         <v>1.63</v>
       </c>
       <c r="U84" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V84" t="n">
         <v>0</v>
@@ -16722,7 +16722,7 @@
         <v>28</v>
       </c>
       <c r="Y84" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z84" t="n">
         <v>50</v>
@@ -16746,7 +16746,7 @@
         <v>13</v>
       </c>
       <c r="AG84" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH84" t="n">
         <v>18</v>
@@ -16758,7 +16758,7 @@
         <v>18.5</v>
       </c>
       <c r="AK84" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL84" t="n">
         <v>30</v>
@@ -16782,7 +16782,7 @@
         <v>40</v>
       </c>
       <c r="AS84" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT84" t="n">
         <v>11.5</v>
@@ -16794,7 +16794,7 @@
         <v>18.5</v>
       </c>
       <c r="AW84" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="AX84" t="n">
         <v>11.5</v>
@@ -16803,13 +16803,13 @@
         <v>9.4</v>
       </c>
       <c r="AZ84" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA84" t="n">
         <v>46</v>
       </c>
       <c r="BB84" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC84" t="n">
         <v>14</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -16859,16 +16859,16 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="G85" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H85" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I85" t="n">
         <v>1.4</v>
-      </c>
-      <c r="I85" t="n">
-        <v>1.41</v>
       </c>
       <c r="J85" t="n">
         <v>5.6</v>
@@ -16901,7 +16901,7 @@
         <v>2.36</v>
       </c>
       <c r="T85" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U85" t="n">
         <v>2.08</v>
@@ -16925,7 +16925,7 @@
         <v>12</v>
       </c>
       <c r="AB85" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AC85" t="n">
         <v>13</v>
@@ -16973,7 +16973,7 @@
         <v>10</v>
       </c>
       <c r="AR85" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS85" t="n">
         <v>10.5</v>
@@ -16991,7 +16991,7 @@
         <v>12.5</v>
       </c>
       <c r="AX85" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AY85" t="n">
         <v>21</v>
@@ -17012,7 +17012,7 @@
         <v>38</v>
       </c>
       <c r="BE85" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF85" t="n">
         <v>42</v>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="G86" t="n">
         <v>4.1</v>
@@ -17062,13 +17062,13 @@
         <v>1.85</v>
       </c>
       <c r="I86" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="J86" t="n">
         <v>4.4</v>
       </c>
       <c r="K86" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -17083,7 +17083,7 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q86" t="n">
         <v>1.39</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -17283,13 +17283,13 @@
         <v>2.36</v>
       </c>
       <c r="R87" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S87" t="n">
         <v>4.7</v>
       </c>
       <c r="T87" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U87" t="n">
         <v>1.84</v>
@@ -17349,7 +17349,7 @@
         <v>190</v>
       </c>
       <c r="AN87" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO87" t="n">
         <v>95</v>
@@ -17361,7 +17361,7 @@
         <v>10.5</v>
       </c>
       <c r="AR87" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AS87" t="n">
         <v>11</v>
@@ -17376,7 +17376,7 @@
         <v>15</v>
       </c>
       <c r="AW87" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="AX87" t="n">
         <v>10.5</v>
@@ -17391,10 +17391,10 @@
         <v>65</v>
       </c>
       <c r="BB87" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BC87" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD87" t="n">
         <v>10</v>
@@ -17406,11 +17406,11 @@
         <v>20</v>
       </c>
       <c r="BG87" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -17441,7 +17441,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G88" t="n">
         <v>1.85</v>
@@ -17471,10 +17471,10 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R88" t="n">
         <v>0</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -18026,7 +18026,7 @@
         <v>1.54</v>
       </c>
       <c r="G91" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="H91" t="n">
         <v>6.2</v>
@@ -18035,10 +18035,10 @@
         <v>8.6</v>
       </c>
       <c r="J91" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="K91" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -18217,7 +18217,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="G92" t="n">
         <v>8</v>
@@ -18226,7 +18226,7 @@
         <v>1.5</v>
       </c>
       <c r="I92" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="J92" t="n">
         <v>4.6</v>
@@ -18250,7 +18250,7 @@
         <v>2.3</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -18411,22 +18411,22 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G93" t="n">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="H93" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I93" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J93" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K93" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -18441,10 +18441,10 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="Q93" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="R93" t="n">
         <v>0</v>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -18802,7 +18802,7 @@
         <v>2.74</v>
       </c>
       <c r="G95" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="H95" t="n">
         <v>2.56</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -19023,7 +19023,7 @@
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q96" t="n">
         <v>1.6</v>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -19196,7 +19196,7 @@
         <v>1.09</v>
       </c>
       <c r="I97" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="J97" t="n">
         <v>9.199999999999999</v>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -19387,7 +19387,7 @@
         <v>3.5</v>
       </c>
       <c r="H98" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="I98" t="n">
         <v>2.96</v>
@@ -19396,7 +19396,7 @@
         <v>3.45</v>
       </c>
       <c r="K98" t="n">
-        <v>6.8</v>
+        <v>950</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -19411,7 +19411,7 @@
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="Q98" t="n">
         <v>1.51</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -19575,22 +19575,22 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G99" t="n">
         <v>1.77</v>
       </c>
       <c r="H99" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I99" t="n">
         <v>5.8</v>
       </c>
       <c r="J99" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K99" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -19605,10 +19605,10 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q99" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R99" t="n">
         <v>0</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -19772,7 +19772,7 @@
         <v>1.87</v>
       </c>
       <c r="G100" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H100" t="n">
         <v>3.85</v>
@@ -19799,7 +19799,7 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="Q100" t="n">
         <v>1.51</v>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -19963,19 +19963,19 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="G101" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H101" t="n">
         <v>10.5</v>
       </c>
       <c r="I101" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="J101" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="K101" t="n">
         <v>4.9</v>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -20166,13 +20166,13 @@
         <v>3.05</v>
       </c>
       <c r="I102" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="J102" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="K102" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -20354,19 +20354,19 @@
         <v>3.3</v>
       </c>
       <c r="G103" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="H103" t="n">
         <v>2.5</v>
       </c>
       <c r="I103" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="J103" t="n">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="K103" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -20381,7 +20381,7 @@
         <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Q103" t="n">
         <v>2.6</v>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -20560,7 +20560,7 @@
         <v>3.15</v>
       </c>
       <c r="K104" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -20936,19 +20936,19 @@
         <v>2.74</v>
       </c>
       <c r="G106" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H106" t="n">
         <v>2.76</v>
       </c>
       <c r="I106" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="J106" t="n">
         <v>1.03</v>
       </c>
       <c r="K106" t="n">
-        <v>3.6</v>
+        <v>950</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -21157,7 +21157,7 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q107" t="n">
         <v>1.54</v>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -21484,7 +21484,7 @@
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -21678,7 +21678,7 @@
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -21872,7 +21872,7 @@
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -21903,7 +21903,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="G111" t="n">
         <v>2.44</v>
@@ -21918,7 +21918,7 @@
         <v>2.92</v>
       </c>
       <c r="K111" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -22244,7 +22244,7 @@
         <v>28</v>
       </c>
       <c r="BC112" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BD112" t="n">
         <v>36</v>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -22291,10 +22291,10 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G113" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H113" t="n">
         <v>4</v>
@@ -22321,10 +22321,10 @@
         <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q113" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R113" t="n">
         <v>0</v>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -22648,7 +22648,7 @@
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -22688,7 +22688,7 @@
         <v>2.48</v>
       </c>
       <c r="I115" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J115" t="n">
         <v>3.3</v>
@@ -22829,7 +22829,7 @@
         <v>25</v>
       </c>
       <c r="BD115" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="BE115" t="n">
         <v>48</v>
@@ -22842,7 +22842,7 @@
       </c>
       <c r="BH115" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -22879,7 +22879,7 @@
         <v>2.48</v>
       </c>
       <c r="H116" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I116" t="n">
         <v>3.95</v>
@@ -22888,7 +22888,7 @@
         <v>3.1</v>
       </c>
       <c r="K116" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -22906,7 +22906,7 @@
         <v>1.7</v>
       </c>
       <c r="Q116" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R116" t="n">
         <v>0</v>
@@ -23036,7 +23036,7 @@
       </c>
       <c r="BH116" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -23070,10 +23070,10 @@
         <v>5.4</v>
       </c>
       <c r="G117" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H117" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="I117" t="n">
         <v>1.66</v>
@@ -23082,7 +23082,7 @@
         <v>4.5</v>
       </c>
       <c r="K117" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -23230,7 +23230,7 @@
       </c>
       <c r="BH117" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -23306,7 +23306,7 @@
         <v>1.96</v>
       </c>
       <c r="U118" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V118" t="n">
         <v>0</v>
@@ -23333,7 +23333,7 @@
         <v>12.5</v>
       </c>
       <c r="AD118" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE118" t="n">
         <v>170</v>
@@ -23378,7 +23378,7 @@
         <v>8.6</v>
       </c>
       <c r="AS118" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT118" t="n">
         <v>7.8</v>
@@ -23402,7 +23402,7 @@
         <v>21</v>
       </c>
       <c r="BA118" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB118" t="n">
         <v>10</v>
@@ -23420,11 +23420,11 @@
         <v>5.2</v>
       </c>
       <c r="BG118" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH118" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -23455,22 +23455,22 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="G119" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="H119" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="I119" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="J119" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="K119" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -23485,7 +23485,7 @@
         <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q119" t="n">
         <v>1.49</v>
@@ -23618,7 +23618,7 @@
       </c>
       <c r="BH119" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -23664,7 +23664,7 @@
         <v>2.76</v>
       </c>
       <c r="K120" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
@@ -23812,7 +23812,7 @@
       </c>
       <c r="BH120" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -24006,7 +24006,7 @@
       </c>
       <c r="BH121" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -24200,7 +24200,7 @@
       </c>
       <c r="BH122" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -24237,16 +24237,16 @@
         <v>3.6</v>
       </c>
       <c r="H123" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="I123" t="n">
-        <v>4.2</v>
+        <v>420</v>
       </c>
       <c r="J123" t="n">
         <v>2.48</v>
       </c>
       <c r="K123" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="BH123" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -24588,7 +24588,7 @@
       </c>
       <c r="BH124" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -24619,22 +24619,22 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G125" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="H125" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="I125" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="J125" t="n">
         <v>3.2</v>
       </c>
       <c r="K125" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -24649,10 +24649,10 @@
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q125" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="R125" t="n">
         <v>0</v>
@@ -24782,7 +24782,7 @@
       </c>
       <c r="BH125" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -24816,7 +24816,7 @@
         <v>4</v>
       </c>
       <c r="G126" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="H126" t="n">
         <v>1.99</v>
@@ -24843,7 +24843,7 @@
         <v>1.37</v>
       </c>
       <c r="P126" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q126" t="n">
         <v>2.02</v>
@@ -24861,10 +24861,10 @@
         <v>1.01</v>
       </c>
       <c r="V126" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W126" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X126" t="n">
         <v>15</v>
@@ -24976,7 +24976,7 @@
       </c>
       <c r="BH126" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -25010,10 +25010,10 @@
         <v>2.26</v>
       </c>
       <c r="G127" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H127" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I127" t="n">
         <v>4.1</v>
@@ -25170,7 +25170,7 @@
       </c>
       <c r="BH127" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -25201,19 +25201,19 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="G128" t="n">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="H128" t="n">
         <v>2.8</v>
       </c>
       <c r="I128" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J128" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="K128" t="n">
         <v>3.8</v>
@@ -25255,28 +25255,28 @@
         <v>0</v>
       </c>
       <c r="X128" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Y128" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z128" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AA128" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB128" t="n">
         <v>14</v>
       </c>
       <c r="AC128" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD128" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE128" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF128" t="n">
         <v>22</v>
@@ -25285,76 +25285,76 @@
         <v>14.5</v>
       </c>
       <c r="AH128" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI128" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ128" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK128" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL128" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM128" t="n">
         <v>1000</v>
       </c>
       <c r="AN128" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AO128" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AP128" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ128" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AR128" t="n">
-        <v>5.7</v>
+        <v>15</v>
       </c>
       <c r="AS128" t="n">
-        <v>6.6</v>
+        <v>32</v>
       </c>
       <c r="AT128" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AU128" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV128" t="n">
-        <v>4.9</v>
+        <v>9.6</v>
       </c>
       <c r="AW128" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AX128" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AY128" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AZ128" t="n">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA128" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="BB128" t="n">
-        <v>6.4</v>
+        <v>3.95</v>
       </c>
       <c r="BC128" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="BD128" t="n">
-        <v>6.4</v>
+        <v>3.95</v>
       </c>
       <c r="BE128" t="n">
-        <v>7.2</v>
+        <v>55</v>
       </c>
       <c r="BF128" t="n">
         <v>15.5</v>
@@ -25364,7 +25364,7 @@
       </c>
       <c r="BH128" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -25398,16 +25398,16 @@
         <v>2.5</v>
       </c>
       <c r="G129" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H129" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I129" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J129" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K129" t="n">
         <v>3.8</v>
@@ -25428,7 +25428,7 @@
         <v>2</v>
       </c>
       <c r="Q129" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R129" t="n">
         <v>0</v>
@@ -25437,10 +25437,10 @@
         <v>0</v>
       </c>
       <c r="T129" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U129" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="V129" t="n">
         <v>0</v>
@@ -25449,7 +25449,7 @@
         <v>0</v>
       </c>
       <c r="X129" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y129" t="n">
         <v>15</v>
@@ -25479,13 +25479,13 @@
         <v>14</v>
       </c>
       <c r="AH129" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI129" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ129" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK129" t="n">
         <v>32</v>
@@ -25497,58 +25497,58 @@
         <v>1000</v>
       </c>
       <c r="AN129" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO129" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP129" t="n">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="AQ129" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR129" t="n">
-        <v>4.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS129" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT129" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU129" t="n">
         <v>7</v>
       </c>
       <c r="AV129" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="AW129" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AX129" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AY129" t="n">
         <v>10</v>
       </c>
       <c r="AZ129" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA129" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BB129" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BC129" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD129" t="n">
         <v>4.8</v>
       </c>
-      <c r="BD129" t="n">
-        <v>5</v>
-      </c>
       <c r="BE129" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BF129" t="n">
         <v>16</v>
@@ -25558,7 +25558,7 @@
       </c>
       <c r="BH129" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -25752,7 +25752,7 @@
       </c>
       <c r="BH130" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -25789,7 +25789,7 @@
         <v>3.45</v>
       </c>
       <c r="H131" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I131" t="n">
         <v>2.76</v>
@@ -25816,7 +25816,7 @@
         <v>1.57</v>
       </c>
       <c r="Q131" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R131" t="n">
         <v>0</v>
@@ -25946,7 +25946,7 @@
       </c>
       <c r="BH131" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
